--- a/4.evidence/ITGC/UATテスト結果_REL-2025-050.xlsx
+++ b/4.evidence/ITGC/UATテスト結果_REL-2025-050.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,27 +26,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
       <b val="1"/>
-      <sz val="10"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Yu Gothic"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -55,21 +46,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -77,89 +58,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00888888"/>
-      </left>
-      <right style="thin">
-        <color rgb="00888888"/>
-      </right>
-      <top style="thin">
-        <color rgb="00888888"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00888888"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00888888"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00888888"/>
-      </right>
-      <top style="thin">
-        <color rgb="00888888"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00888888"/>
-      </right>
-      <top style="thin">
-        <color rgb="00888888"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00888888"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00888888"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00888888"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,17 +432,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -551,17 +458,11 @@
           <t>REL番号</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>REL-2025-050</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -569,17 +470,11 @@
           <t>変更件名</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>仕入先マスタ項目拡張</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="3" t="n"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>勘定科目マスタ追加</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -587,17 +482,11 @@
           <t>UAT実施日</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>2025年12月11日</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="3" t="n"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025年04月19日</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -605,17 +494,11 @@
           <t>実施者</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>高橋 美咲 (ACC002)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="3" t="n"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>中村 真理 (ACC004)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -623,17 +506,11 @@
           <t>対象モジュール</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>MM</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="3" t="n"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -641,218 +518,149 @@
           <t>総ケース数</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="3" t="n"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>ケースID</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>ケース名</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>実施日時</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>欠陥ID</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>TC-仕入先-001</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>正常系：既存マスタへの新規項目追加</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TC-勘定科-001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>正常系：新規勘定科目登録</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>2025-12-11 09:30</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025-04-19 09:17</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>TC-仕入先-002</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>正常系：既存データとの互換性確認</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TC-勘定科-002</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>正常系：科目コード重複チェック</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>2025-12-11 10:36</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2025-04-19 09:34</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>TC-仕入先-003</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>境界系：NULL許容動作</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TC-勘定科-003</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>正常系：仕訳登録での使用確認</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>2025-12-11 10:47</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025-04-19 10:51</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>TC-仕入先-004</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>性能系：5000件マスタ処理</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>2025-12-11 11:20</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>集計</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>総実施: 4 / 合格: 4 / 不合格: 0</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A6:B6"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>